--- a/rsvp_forms/009_sponsor_briefing_breakfast_rsvp_form--rsvp_forms.xlsx
+++ b/rsvp_forms/009_sponsor_briefing_breakfast_rsvp_form--rsvp_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_title</t>
+          <t>Sponsor Briefing Breakfast RSVP Form</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_dietary_preferences</t>
+          <t>Dietary Preferences</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_attendance</t>
+          <t>Attendance</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_email</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_phone</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_comments</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_date</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_time</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_rsvp_form_id</t>
+          <t>RSVP Form ID</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_form_type</t>
+          <t>Form Type</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_comments</t>
+          <t>sponsor_briefing_breakfast_rsvp_form_comments_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_comments</t>
+          <t>Sponsor Briefing Breakfast Rsvp Form Comments 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_venue</t>
+          <t>Venue</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_notes</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_additional_comments</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_form_id</t>
+          <t>Form ID</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_form_version</t>
+          <t>Form Version</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,174 +916,13 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_form_name</t>
+          <t>Form Name</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_last_updated_by</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_last_updated_by</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_last_updated_at</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_last_updated_at</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_last_updated_by</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_last_updated_by</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_last_updated_at</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_last_updated_at</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_last_updated_by</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_last_updated_by</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_last_updated_at</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_last_updated_at</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_last_updated_by</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>sponsor_briefing_breakfast_rsvp_form_last_updated_by</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -1102,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'vegetarian'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'vegetarian'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -1148,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'vegan'}</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'vegan'}</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'special_diet'}</t>
+          <t>special_diet</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'special_diet'}</t>
+          <t>Special Diet</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'hint':_'please_specify'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'other', 'hint': 'Please specify'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'sponsor_briefing_breakfast_rsvp'}</t>
+          <t>sponsor_briefing_breakfast_rsvp</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'sponsor_briefing_breakfast_rsvp'}</t>
+          <t>Sponsor Briefing Breakfast RSVP</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
